--- a/data/TTN/最新版班表/2026-10/TTN_TM.xlsx
+++ b/data/TTN/最新版班表/2026-10/TTN_TM.xlsx
@@ -890,18 +890,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G7" s="1" t="inlineStr">
@@ -920,11 +916,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="I7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J7" s="1" t="inlineStr">
@@ -951,18 +945,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="M7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="N7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
@@ -981,11 +971,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Q7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R7" s="1" t="inlineStr">
@@ -1004,11 +992,9 @@
 9:35</t>
         </is>
       </c>
-      <c r="T7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="U7" s="1" t="inlineStr">
@@ -1035,25 +1021,19 @@
 8:00</t>
         </is>
       </c>
-      <c r="X7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="Y7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="Z7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AA7" s="1" t="inlineStr">
@@ -1100,11 +1080,9 @@
           <t>汪莉芳</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
@@ -1139,18 +1117,14 @@
 8:22</t>
         </is>
       </c>
-      <c r="H8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="I8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J8" s="1" t="inlineStr">
@@ -1169,18 +1143,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="L8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="M8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="N8" s="1" t="inlineStr">
@@ -1207,11 +1177,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Q8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr">
@@ -1238,11 +1206,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="U8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="V8" s="1" t="inlineStr">
@@ -1278,18 +1244,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AA8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AB8" s="1" t="inlineStr">
@@ -1352,18 +1314,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H9" s="1" t="inlineStr">
@@ -1399,11 +1357,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="L9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="M9" s="1" t="inlineStr">
@@ -1422,11 +1378,9 @@
 8:02</t>
         </is>
       </c>
-      <c r="O9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr">
@@ -1453,11 +1407,9 @@
 9:12</t>
         </is>
       </c>
-      <c r="S9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="T9" s="1" t="inlineStr">
@@ -1484,18 +1436,14 @@
 8:32</t>
         </is>
       </c>
-      <c r="W9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="X9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y9" s="1" t="inlineStr">
@@ -1514,18 +1462,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AB9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC9" s="1" t="inlineStr">
@@ -1572,11 +1516,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="F10" s="1" t="inlineStr">
@@ -1595,18 +1537,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="H10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="I10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J10" s="1" t="inlineStr">
@@ -1641,18 +1579,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="N10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="O10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr">
@@ -1671,11 +1605,9 @@
 8:02</t>
         </is>
       </c>
-      <c r="R10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="S10" s="1" t="inlineStr">
@@ -1702,11 +1634,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="V10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W10" s="1" t="inlineStr">
@@ -1726,11 +1656,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Y10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Z10" s="1" t="inlineStr">
@@ -1765,11 +1693,9 @@
 8:35</t>
         </is>
       </c>
-      <c r="AD10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -1792,18 +1718,14 @@
 8:07</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="F11" s="1" t="inlineStr">
@@ -1839,11 +1761,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="K11" s="1" t="inlineStr">
@@ -1878,11 +1798,9 @@
 8:07</t>
         </is>
       </c>
-      <c r="O11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr">
@@ -1917,18 +1835,14 @@
 8:22</t>
         </is>
       </c>
-      <c r="T11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="U11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="V11" s="1" t="inlineStr">
@@ -1947,11 +1861,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="X11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y11" s="1" t="inlineStr">
@@ -1979,11 +1891,9 @@
 9:42</t>
         </is>
       </c>
-      <c r="AB11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AC11" s="1" t="inlineStr">
@@ -2022,18 +1932,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="F12" s="1" t="inlineStr">
@@ -2060,11 +1966,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="I12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J12" s="1" t="inlineStr">
@@ -2083,18 +1987,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="L12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="M12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="N12" s="1" t="inlineStr">
@@ -2121,11 +2021,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Q12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R12" s="1" t="inlineStr">
@@ -2160,11 +2058,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="V12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W12" s="1" t="inlineStr">
@@ -2192,18 +2088,14 @@
 8:05</t>
         </is>
       </c>
-      <c r="Z12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AA12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AB12" s="1" t="inlineStr">
@@ -2258,11 +2150,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="F13" s="1" t="inlineStr">
@@ -2281,25 +2171,19 @@
 8:07</t>
         </is>
       </c>
-      <c r="H13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="I13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="K13" s="1" t="inlineStr">
@@ -2318,11 +2202,9 @@
 8:22</t>
         </is>
       </c>
-      <c r="M13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="N13" s="1" t="inlineStr">
@@ -2349,11 +2231,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Q13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R13" s="1" t="inlineStr">
@@ -2388,11 +2268,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="V13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W13" s="1" t="inlineStr">
@@ -2428,18 +2306,14 @@
 8:22</t>
         </is>
       </c>
-      <c r="AA13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AB13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC13" s="1" t="inlineStr">
@@ -2478,18 +2352,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="F14" s="1" t="inlineStr">
@@ -2533,11 +2403,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr">
@@ -2572,11 +2440,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="P14" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q14" s="1" t="inlineStr">
@@ -2595,18 +2461,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="S14" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="T14" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="U14" s="1" t="inlineStr">
@@ -2633,18 +2495,14 @@
 8:10</t>
         </is>
       </c>
-      <c r="X14" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="Y14" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Z14" s="1" t="inlineStr">
@@ -2671,11 +2529,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AC14" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AD14" s="1" t="inlineStr">
@@ -2722,18 +2578,14 @@
 9:40</t>
         </is>
       </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="G15" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H15" s="1" t="inlineStr">
@@ -2761,11 +2613,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L15" s="1" t="inlineStr">
@@ -2792,11 +2642,9 @@
 9:40</t>
         </is>
       </c>
-      <c r="O15" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr">
@@ -2831,18 +2679,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="T15" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="U15" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="V15" s="1" t="inlineStr">
@@ -2886,11 +2730,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA15" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AB15" s="1" t="inlineStr">
@@ -2909,11 +2751,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD15" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -2928,11 +2768,9 @@
           <t>李育真</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
@@ -2967,18 +2805,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="H16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="I16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J16" s="1" t="inlineStr">
@@ -2989,11 +2823,9 @@
 8:27</t>
         </is>
       </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L16" s="1" t="inlineStr">
@@ -3004,11 +2836,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="M16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="N16" s="1" t="inlineStr">
@@ -3051,11 +2881,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="S16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="T16" s="1" t="inlineStr">
@@ -3082,18 +2910,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="W16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="X16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y16" s="1" t="inlineStr">
@@ -3112,11 +2936,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AB16" s="1" t="inlineStr">
@@ -3180,18 +3002,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H17" s="1" t="inlineStr">
@@ -3235,18 +3053,14 @@
 9:40</t>
         </is>
       </c>
-      <c r="M17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="N17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
@@ -3273,18 +3087,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="R17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="S17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="T17" s="1" t="inlineStr">
@@ -3328,18 +3138,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="Y17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="Z17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="AA17" s="1" t="inlineStr">
@@ -3366,11 +3172,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -3401,18 +3205,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="E18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="F18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G18" s="1" t="inlineStr">
@@ -3431,11 +3231,9 @@
 9:52</t>
         </is>
       </c>
-      <c r="I18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J18" s="1" t="inlineStr">
@@ -3454,17 +3252,15 @@
 8:00</t>
         </is>
       </c>
-      <c r="L18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="M18" s="1" t="inlineStr">
         <is>
           <t>5:00
-E008g
+E008G
 13:30
 8:30</t>
         </is>
@@ -3485,11 +3281,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="P18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q18" s="1" t="inlineStr">
@@ -3524,18 +3318,14 @@
 8:10</t>
         </is>
       </c>
-      <c r="U18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="V18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W18" s="1" t="inlineStr">
@@ -3563,11 +3353,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AA18" s="1" t="inlineStr">
@@ -3586,11 +3374,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AC18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AD18" s="1" t="inlineStr">
@@ -3629,18 +3415,14 @@
 9:42</t>
         </is>
       </c>
-      <c r="E19" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="F19" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G19" s="1" t="inlineStr">
@@ -3668,11 +3450,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="J19" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="K19" s="1" t="inlineStr">
@@ -3715,11 +3495,9 @@
 9:35</t>
         </is>
       </c>
-      <c r="P19" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q19" s="1" t="inlineStr">
@@ -3738,18 +3516,14 @@
 9:35</t>
         </is>
       </c>
-      <c r="S19" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="T19" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="U19" s="1" t="inlineStr">
@@ -3793,11 +3567,9 @@
 8:22</t>
         </is>
       </c>
-      <c r="Z19" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AA19" s="1" t="inlineStr">
@@ -3824,11 +3596,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD19" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -3851,11 +3621,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
@@ -3882,11 +3650,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="H20" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="I20" s="1" t="inlineStr">
@@ -3922,18 +3688,14 @@
 8:10</t>
         </is>
       </c>
-      <c r="M20" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="N20" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
@@ -3968,11 +3730,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="S20" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="T20" s="1" t="inlineStr">
@@ -3991,11 +3751,9 @@
 8:27</t>
         </is>
       </c>
-      <c r="V20" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W20" s="1" t="inlineStr">
@@ -4015,11 +3773,9 @@
 8:12</t>
         </is>
       </c>
-      <c r="Y20" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Z20" s="1" t="inlineStr">
@@ -4046,11 +3802,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AC20" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AD20" s="1" t="inlineStr">
@@ -4081,18 +3835,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="F21" s="1" t="inlineStr">
@@ -4119,11 +3869,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="I21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J21" s="1" t="inlineStr">
@@ -4134,11 +3882,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L21" s="1" t="inlineStr">
@@ -4173,18 +3919,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="P21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="Q21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R21" s="1" t="inlineStr">
@@ -4211,11 +3953,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="U21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="V21" s="1" t="inlineStr">
@@ -4243,18 +3983,14 @@
 9:50</t>
         </is>
       </c>
-      <c r="Y21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="Z21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AA21" s="1" t="inlineStr">
@@ -4309,11 +4045,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
@@ -4324,11 +4058,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G22" s="1" t="inlineStr">
@@ -4347,11 +4079,9 @@
 8:20</t>
         </is>
       </c>
-      <c r="I22" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J22" s="1" t="inlineStr">
@@ -4378,11 +4108,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="M22" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="N22" s="1" t="inlineStr">
@@ -4401,18 +4129,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="P22" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="Q22" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R22" s="1" t="inlineStr">
@@ -4447,11 +4171,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="V22" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W22" s="1" t="inlineStr">
@@ -4479,18 +4201,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z22" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AA22" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AB22" s="1" t="inlineStr">
@@ -4529,11 +4247,9 @@
           <t>陳坤妏</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
@@ -4568,11 +4284,9 @@
 8:27</t>
         </is>
       </c>
-      <c r="H23" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="I23" s="1" t="inlineStr">
@@ -4600,18 +4314,14 @@
 8:15</t>
         </is>
       </c>
-      <c r="L23" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="M23" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="N23" s="1" t="inlineStr">
@@ -4646,11 +4356,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="R23" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="S23" s="1" t="inlineStr">
@@ -4685,18 +4393,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="W23" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="X23" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y23" s="1" t="inlineStr">
@@ -4715,18 +4419,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA23" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AB23" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC23" s="1" t="inlineStr">
@@ -4773,39 +4473,29 @@
 8:00</t>
         </is>
       </c>
-      <c r="E24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="F24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="H24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="I24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J24" s="1" t="inlineStr">
@@ -4840,11 +4530,9 @@
 8:07</t>
         </is>
       </c>
-      <c r="N24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
@@ -4855,11 +4543,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="P24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q24" s="1" t="inlineStr">
@@ -4878,11 +4564,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="S24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="T24" s="1" t="inlineStr">
@@ -4901,11 +4585,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="V24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W24" s="1" t="inlineStr">
@@ -4916,11 +4598,9 @@
 8:15</t>
         </is>
       </c>
-      <c r="X24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y24" s="1" t="inlineStr">
@@ -4947,18 +4627,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="AB24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AC24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AD24" s="1" t="inlineStr">
@@ -5013,18 +4689,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="H25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="I25" s="1" t="inlineStr">
@@ -5068,18 +4740,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="N25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="O25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr">
@@ -5098,11 +4766,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="R25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="S25" s="1" t="inlineStr">
@@ -5137,11 +4803,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="W25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="X25" s="1" t="inlineStr">
@@ -5169,18 +4833,14 @@
 9:42</t>
         </is>
       </c>
-      <c r="AA25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AB25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC25" s="1" t="inlineStr">
@@ -5219,11 +4879,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="D26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
@@ -5250,18 +4908,14 @@
 8:57</t>
         </is>
       </c>
-      <c r="H26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="I26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J26" s="1" t="inlineStr">
@@ -5280,11 +4934,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="L26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="M26" s="1" t="inlineStr">
@@ -5303,11 +4955,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="O26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr">
@@ -5326,18 +4976,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="R26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="S26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="T26" s="1" t="inlineStr">
@@ -5372,11 +5018,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="X26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y26" s="1" t="inlineStr">
@@ -5387,11 +5031,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AA26" s="1" t="inlineStr">
@@ -5418,11 +5060,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -5445,18 +5085,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="F27" s="1" t="inlineStr">
@@ -5492,11 +5128,9 @@
 9:30</t>
         </is>
       </c>
-      <c r="J27" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="K27" s="1" t="inlineStr">
@@ -5539,11 +5173,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="P27" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q27" s="1" t="inlineStr">
@@ -5562,18 +5194,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="S27" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="T27" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="U27" s="1" t="inlineStr">
@@ -5617,18 +5245,14 @@
 9:57</t>
         </is>
       </c>
-      <c r="Z27" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AA27" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AB27" s="1" t="inlineStr">
@@ -5667,11 +5291,9 @@
           <t>林怡宏</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
@@ -5706,11 +5328,9 @@
 9:55</t>
         </is>
       </c>
-      <c r="H28" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="I28" s="1" t="inlineStr">
@@ -5730,11 +5350,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L28" s="1" t="inlineStr">
@@ -5753,11 +5371,9 @@
 9:35</t>
         </is>
       </c>
-      <c r="N28" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
@@ -5784,18 +5400,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="R28" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="S28" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="T28" s="1" t="inlineStr">
@@ -5830,25 +5442,19 @@
 8:00</t>
         </is>
       </c>
-      <c r="X28" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="Y28" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="Z28" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AA28" s="1" t="inlineStr">
@@ -5919,18 +5525,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H29" s="1" t="inlineStr">
@@ -5941,11 +5543,9 @@
 8:10</t>
         </is>
       </c>
-      <c r="I29" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J29" s="1" t="inlineStr">
@@ -5956,18 +5556,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="L29" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="M29" s="1" t="inlineStr">
@@ -6002,18 +5598,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="Q29" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="R29" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="S29" s="1" t="inlineStr">
@@ -6032,11 +5624,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="U29" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="V29" s="1" t="inlineStr">
@@ -6064,11 +5654,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Y29" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Z29" s="1" t="inlineStr">
@@ -6103,11 +5691,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD29" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -6130,11 +5716,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="D30" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
@@ -6153,11 +5737,9 @@
 8:22</t>
         </is>
       </c>
-      <c r="G30" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H30" s="1" t="inlineStr">
@@ -6168,11 +5750,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="I30" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J30" s="1" t="inlineStr">
@@ -6183,18 +5763,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="L30" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="M30" s="1" t="inlineStr">
@@ -6237,18 +5813,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="R30" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="S30" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="T30" s="1" t="inlineStr">
@@ -6275,11 +5847,9 @@
 8:42</t>
         </is>
       </c>
-      <c r="W30" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="X30" s="1" t="inlineStr">
@@ -6299,18 +5869,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z30" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AA30" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AB30" s="1" t="inlineStr">
@@ -6357,11 +5923,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr">
@@ -6388,11 +5952,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="H31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="I31" s="1" t="inlineStr">
@@ -6412,11 +5974,9 @@
 8:12</t>
         </is>
       </c>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L31" s="1" t="inlineStr">
@@ -6451,11 +6011,9 @@
 8:12</t>
         </is>
       </c>
-      <c r="P31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q31" s="1" t="inlineStr">
@@ -6474,18 +6032,14 @@
 9:40</t>
         </is>
       </c>
-      <c r="S31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="T31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="U31" s="1" t="inlineStr">
@@ -6521,11 +6075,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Y31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Z31" s="1" t="inlineStr">
@@ -6560,11 +6112,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -6587,11 +6137,9 @@
 8:32</t>
         </is>
       </c>
-      <c r="D32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr">
@@ -6610,11 +6158,9 @@
 8:22</t>
         </is>
       </c>
-      <c r="G32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H32" s="1" t="inlineStr">
@@ -6650,18 +6196,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="L32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="M32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="N32" s="1" t="inlineStr">
@@ -6696,11 +6238,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="R32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="S32" s="1" t="inlineStr">
@@ -6735,18 +6275,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="W32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="X32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y32" s="1" t="inlineStr">
@@ -6773,18 +6309,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="AB32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AC32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AD32" s="1" t="inlineStr">
@@ -6815,11 +6347,9 @@
 8:12</t>
         </is>
       </c>
-      <c r="D33" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr">
@@ -6838,11 +6368,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="G33" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H33" s="1" t="inlineStr">
@@ -6894,18 +6422,14 @@
 9:40</t>
         </is>
       </c>
-      <c r="N33" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="O33" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr">
@@ -6924,11 +6448,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="R33" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="S33" s="1" t="inlineStr">
@@ -6947,11 +6469,9 @@
 9:35</t>
         </is>
       </c>
-      <c r="U33" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="V33" s="1" t="inlineStr">
@@ -6979,11 +6499,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Y33" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Z33" s="1" t="inlineStr">
@@ -7018,11 +6536,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD33" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -7053,18 +6569,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="E34" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="F34" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G34" s="1" t="inlineStr">
@@ -7083,11 +6595,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="I34" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J34" s="1" t="inlineStr">
@@ -7106,11 +6616,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="L34" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="M34" s="1" t="inlineStr">
@@ -7129,11 +6637,9 @@
 8:02</t>
         </is>
       </c>
-      <c r="O34" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr">
@@ -7184,18 +6690,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="V34" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="W34" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="X34" s="1" t="inlineStr">
@@ -7231,18 +6733,14 @@
 8:22</t>
         </is>
       </c>
-      <c r="AB34" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AC34" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AD34" s="1" t="inlineStr">
@@ -7265,11 +6763,9 @@
           <t>林淮震</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
@@ -7288,11 +6784,9 @@
 8:10</t>
         </is>
       </c>
-      <c r="F35" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G35" s="1" t="inlineStr">
@@ -7344,18 +6838,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="M35" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="N35" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
@@ -7398,11 +6888,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="T35" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="U35" s="1" t="inlineStr">
@@ -7421,11 +6909,9 @@
 9:17</t>
         </is>
       </c>
-      <c r="W35" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="X35" s="1" t="inlineStr">
@@ -7469,18 +6955,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="AC35" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AD35" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -7503,18 +6985,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="E36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="F36" s="1" t="inlineStr">
@@ -7525,25 +7003,19 @@
 8:00</t>
         </is>
       </c>
-      <c r="G36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="H36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="I36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J36" s="1" t="inlineStr">
@@ -7554,11 +7026,9 @@
 8:12</t>
         </is>
       </c>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L36" s="1" t="inlineStr">
@@ -7577,11 +7047,9 @@
 8:22</t>
         </is>
       </c>
-      <c r="N36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
@@ -7624,18 +7092,14 @@
 8:10</t>
         </is>
       </c>
-      <c r="T36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="U36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="V36" s="1" t="inlineStr">
@@ -7654,11 +7118,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="X36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y36" s="1" t="inlineStr">
@@ -7677,18 +7139,14 @@
 8:22</t>
         </is>
       </c>
-      <c r="AA36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AB36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC36" s="1" t="inlineStr">
@@ -7735,18 +7193,14 @@
 8:22</t>
         </is>
       </c>
-      <c r="E37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="F37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G37" s="1" t="inlineStr">
@@ -7765,11 +7219,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="I37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J37" s="1" t="inlineStr">
@@ -7780,11 +7232,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L37" s="1" t="inlineStr">
@@ -7811,11 +7261,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="O37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr">
@@ -7834,11 +7282,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="R37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="S37" s="1" t="inlineStr">
@@ -7873,11 +7319,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="W37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="X37" s="1" t="inlineStr">
@@ -7897,11 +7341,9 @@
 9:07</t>
         </is>
       </c>
-      <c r="Z37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AA37" s="1" t="inlineStr">
@@ -7920,11 +7362,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AC37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AD37" s="1" t="inlineStr">
@@ -7947,11 +7387,9 @@
           <t>侯美玉</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
@@ -7970,11 +7408,9 @@
 9:42</t>
         </is>
       </c>
-      <c r="F38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
@@ -8002,11 +7438,9 @@
 8:05</t>
         </is>
       </c>
-      <c r="J38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="K38" s="1" t="inlineStr">
@@ -8033,11 +7467,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="N38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
@@ -8064,11 +7496,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="R38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="S38" s="1" t="inlineStr">
@@ -8095,11 +7525,9 @@
 9:35</t>
         </is>
       </c>
-      <c r="V38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W38" s="1" t="inlineStr">
@@ -8110,11 +7538,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="X38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y38" s="1" t="inlineStr">
@@ -8141,11 +7567,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AB38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AC38" s="1" t="inlineStr">
@@ -8156,11 +7580,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -8175,18 +7597,14 @@
           <t>林蕙儀</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="E39" s="1" t="inlineStr">
@@ -8205,11 +7623,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="G39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H39" s="1" t="inlineStr">
@@ -8237,18 +7653,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="L39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="M39" s="1" t="inlineStr">
@@ -8283,11 +7695,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Q39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R39" s="1" t="inlineStr">
@@ -8330,18 +7740,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="W39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="X39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y39" s="1" t="inlineStr">
@@ -8360,25 +7766,19 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="AB39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AC39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AD39" s="1" t="inlineStr">
@@ -8401,11 +7801,9 @@
           <t>徐玓瑋</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
@@ -8424,11 +7822,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="F40" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr">
@@ -8447,11 +7843,9 @@
 8:27</t>
         </is>
       </c>
-      <c r="I40" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J40" s="1" t="inlineStr">
@@ -8470,18 +7864,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="L40" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="M40" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="N40" s="1" t="inlineStr">
@@ -8524,11 +7914,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="S40" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="T40" s="1" t="inlineStr">
@@ -8547,11 +7935,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="V40" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W40" s="1" t="inlineStr">
@@ -8587,18 +7973,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA40" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AB40" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC40" s="1" t="inlineStr">
@@ -8629,11 +8011,9 @@
           <t>陳君煒</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
@@ -8668,18 +8048,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="H41" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="I41" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J41" s="1" t="inlineStr">
@@ -8706,18 +8082,14 @@
 8:22</t>
         </is>
       </c>
-      <c r="M41" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="N41" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr">
@@ -8760,18 +8132,14 @@
 8:16</t>
         </is>
       </c>
-      <c r="T41" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="U41" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="V41" s="1" t="inlineStr">
@@ -8807,18 +8175,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z41" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AA41" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AB41" s="1" t="inlineStr">
@@ -8837,11 +8201,9 @@
 8:07</t>
         </is>
       </c>
-      <c r="AD41" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
     </row>
@@ -8856,11 +8218,9 @@
           <t>郭曉芸</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
@@ -8887,11 +8247,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="G42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H42" s="1" t="inlineStr">
@@ -8927,11 +8285,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="L42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="M42" s="1" t="inlineStr">
@@ -8958,18 +8314,14 @@
 8:32</t>
         </is>
       </c>
-      <c r="P42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="Q42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R42" s="1" t="inlineStr">
@@ -9004,11 +8356,9 @@
 8:02</t>
         </is>
       </c>
-      <c r="V42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W42" s="1" t="inlineStr">
@@ -9044,11 +8394,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AB42" s="1" t="inlineStr">
@@ -9059,11 +8407,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AC42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AD42" s="1" t="inlineStr">
@@ -9094,11 +8440,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="D43" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
@@ -9125,11 +8469,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="H43" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="I43" s="1" t="inlineStr">
@@ -9157,18 +8499,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="L43" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="M43" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="N43" s="1" t="inlineStr">
@@ -9211,18 +8549,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="S43" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="T43" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="U43" s="1" t="inlineStr">
@@ -9267,11 +8601,9 @@
 9:56</t>
         </is>
       </c>
-      <c r="Z43" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AA43" s="1" t="inlineStr">
@@ -9318,11 +8650,9 @@
           <t>李育瑋</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
@@ -9341,11 +8671,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="F44" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G44" s="1" t="inlineStr">
@@ -9389,18 +8717,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="L44" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="M44" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="N44" s="1" t="inlineStr">
@@ -9427,11 +8751,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Q44" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R44" s="1" t="inlineStr">
@@ -9458,11 +8780,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="U44" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="V44" s="1" t="inlineStr">
@@ -9498,11 +8818,9 @@
 8:14</t>
         </is>
       </c>
-      <c r="Z44" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AA44" s="1" t="inlineStr">
@@ -9521,11 +8839,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AC44" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AD44" s="1" t="inlineStr">
@@ -9556,11 +8872,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="D45" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="E45" s="1" t="inlineStr">
@@ -9587,11 +8901,9 @@
 8:35</t>
         </is>
       </c>
-      <c r="H45" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="I45" s="1" t="inlineStr">
@@ -9619,11 +8931,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="L45" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="M45" s="1" t="inlineStr">
@@ -9642,11 +8952,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="O45" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P45" s="1" t="inlineStr">
@@ -9665,11 +8973,9 @@
 9:17</t>
         </is>
       </c>
-      <c r="R45" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="S45" s="1" t="inlineStr">
@@ -9704,11 +9010,9 @@
 9:40</t>
         </is>
       </c>
-      <c r="W45" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="X45" s="1" t="inlineStr">
@@ -9736,11 +9040,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA45" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AB45" s="1" t="inlineStr">
@@ -9780,11 +9082,9 @@
           <t>陳家豪</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
@@ -9803,11 +9103,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="F46" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G46" s="1" t="inlineStr">
@@ -9835,11 +9133,9 @@
 9:30</t>
         </is>
       </c>
-      <c r="J46" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="K46" s="1" t="inlineStr">
@@ -9874,11 +9170,9 @@
 8:07</t>
         </is>
       </c>
-      <c r="O46" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P46" s="1" t="inlineStr">
@@ -9905,18 +9199,14 @@
 8:15</t>
         </is>
       </c>
-      <c r="S46" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="T46" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="U46" s="1" t="inlineStr">
@@ -9952,11 +9242,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Y46" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Z46" s="1" t="inlineStr">
@@ -9975,25 +9263,19 @@
 8:00</t>
         </is>
       </c>
-      <c r="AB46" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO
-</t>
-        </is>
-      </c>
-      <c r="AC46" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO
-</t>
-        </is>
-      </c>
-      <c r="AD46" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -10024,18 +9306,14 @@
 8:04</t>
         </is>
       </c>
-      <c r="E47" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="F47" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G47" s="1" t="inlineStr">
@@ -10071,11 +9349,9 @@
 9:54</t>
         </is>
       </c>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L47" s="1" t="inlineStr">
@@ -10110,11 +9386,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="P47" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q47" s="1" t="inlineStr">
@@ -10149,18 +9423,14 @@
 8:04</t>
         </is>
       </c>
-      <c r="U47" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="V47" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W47" s="1" t="inlineStr">
@@ -10188,11 +9458,9 @@
 9:25</t>
         </is>
       </c>
-      <c r="Z47" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AA47" s="1" t="inlineStr">
@@ -10219,11 +9487,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD47" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -10254,18 +9520,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="E48" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="F48" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G48" s="1" t="inlineStr">
@@ -10284,11 +9546,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="I48" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J48" s="1" t="inlineStr">
@@ -10299,11 +9559,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L48" s="1" t="inlineStr">
@@ -10330,11 +9588,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="O48" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P48" s="1" t="inlineStr">
@@ -10369,18 +9625,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="T48" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="U48" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="V48" s="1" t="inlineStr">
@@ -10432,18 +9684,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="AB48" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AC48" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AD48" s="1" t="inlineStr">
@@ -10474,11 +9722,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="D49" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="E49" s="1" t="inlineStr">
@@ -10505,11 +9751,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="H49" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="I49" s="1" t="inlineStr">
@@ -10529,18 +9773,14 @@
 8:32</t>
         </is>
       </c>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="L49" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="M49" s="1" t="inlineStr">
@@ -10583,18 +9823,14 @@
 9:44</t>
         </is>
       </c>
-      <c r="R49" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="S49" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="T49" s="1" t="inlineStr">
@@ -10638,11 +9874,9 @@
 9:44</t>
         </is>
       </c>
-      <c r="Y49" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Z49" s="1" t="inlineStr">
@@ -10677,11 +9911,9 @@
 8:02</t>
         </is>
       </c>
-      <c r="AD49" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -10712,11 +9944,9 @@
 9:12</t>
         </is>
       </c>
-      <c r="E50" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="F50" s="1" t="inlineStr">
@@ -10727,11 +9957,9 @@
 9:40</t>
         </is>
       </c>
-      <c r="G50" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H50" s="1" t="inlineStr">
@@ -10775,18 +10003,14 @@
 9:35</t>
         </is>
       </c>
-      <c r="M50" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="N50" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr">
@@ -10813,11 +10037,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="R50" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="S50" s="1" t="inlineStr">
@@ -10844,11 +10066,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="V50" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W50" s="1" t="inlineStr">
@@ -10868,11 +10088,9 @@
 8:02</t>
         </is>
       </c>
-      <c r="Y50" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Z50" s="1" t="inlineStr">
@@ -10883,11 +10101,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA50" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AB50" s="1" t="inlineStr">
@@ -10950,18 +10166,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="F51" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="G51" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H51" s="1" t="inlineStr">
@@ -11005,11 +10217,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="M51" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="N51" s="1" t="inlineStr">
@@ -11028,39 +10238,29 @@
 8:00</t>
         </is>
       </c>
-      <c r="P51" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="Q51" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="R51" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="S51" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="T51" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="U51" s="1" t="inlineStr">
@@ -11104,11 +10304,9 @@
 9:30</t>
         </is>
       </c>
-      <c r="Z51" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AA51" s="1" t="inlineStr">
@@ -11135,11 +10333,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD51" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -11154,11 +10350,9 @@
           <t>楊凱傑</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D52" s="1" t="inlineStr">
@@ -11177,11 +10371,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="F52" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G52" s="1" t="inlineStr">
@@ -11217,11 +10409,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L52" s="1" t="inlineStr">
@@ -11256,11 +10446,9 @@
 8:02</t>
         </is>
       </c>
-      <c r="P52" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q52" s="1" t="inlineStr">
@@ -11271,11 +10459,9 @@
 8:22</t>
         </is>
       </c>
-      <c r="R52" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="S52" s="1" t="inlineStr">
@@ -11294,11 +10480,9 @@
 8:16</t>
         </is>
       </c>
-      <c r="U52" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="V52" s="1" t="inlineStr">
@@ -11317,11 +10501,9 @@
 8:02</t>
         </is>
       </c>
-      <c r="X52" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y52" s="1" t="inlineStr">
@@ -11332,11 +10514,9 @@
 8:12</t>
         </is>
       </c>
-      <c r="Z52" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AA52" s="1" t="inlineStr">
@@ -11355,11 +10535,9 @@
 8:32</t>
         </is>
       </c>
-      <c r="AC52" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AD52" s="1" t="inlineStr">
@@ -11382,11 +10560,9 @@
           <t>黃孟慈</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
@@ -11413,11 +10589,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="G53" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H53" s="1" t="inlineStr">
@@ -11453,11 +10627,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="L53" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="M53" s="1" t="inlineStr">
@@ -11476,11 +10648,9 @@
 9:35</t>
         </is>
       </c>
-      <c r="O53" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P53" s="1" t="inlineStr">
@@ -11507,18 +10677,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="S53" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="T53" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="U53" s="1" t="inlineStr">
@@ -11545,11 +10711,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="X53" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y53" s="1" t="inlineStr">
@@ -11560,18 +10724,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z53" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AA53" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AB53" s="1" t="inlineStr">
@@ -11610,11 +10770,9 @@
           <t>劉芳毓</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D54" s="1" t="inlineStr">
@@ -11633,11 +10791,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="F54" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G54" s="1" t="inlineStr">
@@ -11673,11 +10829,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L54" s="1" t="inlineStr">
@@ -11704,11 +10858,9 @@
 8:32</t>
         </is>
       </c>
-      <c r="O54" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P54" s="1" t="inlineStr">
@@ -11735,18 +10887,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="S54" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="T54" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="U54" s="1" t="inlineStr">
@@ -11790,11 +10938,9 @@
 9:50</t>
         </is>
       </c>
-      <c r="Z54" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AA54" s="1" t="inlineStr">
@@ -11805,11 +10951,9 @@
 8:16</t>
         </is>
       </c>
-      <c r="AB54" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC54" s="1" t="inlineStr">
@@ -11848,18 +10992,14 @@
 9:30</t>
         </is>
       </c>
-      <c r="D55" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="E55" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="F55" s="1" t="inlineStr">
@@ -11903,11 +11043,9 @@
 9:30</t>
         </is>
       </c>
-      <c r="K55" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L55" s="1" t="inlineStr">
@@ -11942,11 +11080,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="P55" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q55" s="1" t="inlineStr">
@@ -11965,18 +11101,14 @@
 8:22</t>
         </is>
       </c>
-      <c r="S55" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="T55" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="U55" s="1" t="inlineStr">
@@ -12012,11 +11144,9 @@
 8:32</t>
         </is>
       </c>
-      <c r="Y55" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Z55" s="1" t="inlineStr">
@@ -12053,11 +11183,9 @@
 9:35</t>
         </is>
       </c>
-      <c r="AD55" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
     </row>
@@ -12072,11 +11200,9 @@
           <t>曾智君</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D56" s="1" t="inlineStr">
@@ -12103,11 +11229,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="G56" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H56" s="1" t="inlineStr">
@@ -12151,11 +11275,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="M56" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="N56" s="1" t="inlineStr">
@@ -12166,11 +11288,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="O56" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P56" s="1" t="inlineStr">
@@ -12205,11 +11325,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="T56" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="U56" s="1" t="inlineStr">
@@ -12228,11 +11346,9 @@
 9:35</t>
         </is>
       </c>
-      <c r="W56" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="X56" s="1" t="inlineStr">
@@ -12260,11 +11376,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA56" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AB56" s="1" t="inlineStr">
@@ -12303,11 +11417,9 @@
           <t>黃祥恩</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D57" s="1" t="inlineStr">
@@ -12334,11 +11446,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="G57" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H57" s="1" t="inlineStr">
@@ -12366,18 +11476,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="L57" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="M57" s="1" t="inlineStr">
@@ -12412,11 +11518,9 @@
 8:45</t>
         </is>
       </c>
-      <c r="Q57" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R57" s="1" t="inlineStr">
@@ -12443,11 +11547,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="U57" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="V57" s="1" t="inlineStr">
@@ -12466,18 +11568,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="X57" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="Y57" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Z57" s="1" t="inlineStr">
@@ -12488,18 +11586,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA57" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO
-</t>
-        </is>
-      </c>
-      <c r="AB57" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC57" s="1" t="inlineStr">
@@ -12546,18 +11640,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="E58" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="F58" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G58" s="1" t="inlineStr">
@@ -12593,11 +11683,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="K58" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L58" s="1" t="inlineStr">
@@ -12632,11 +11720,9 @@
 8:07</t>
         </is>
       </c>
-      <c r="P58" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q58" s="1" t="inlineStr">
@@ -12671,18 +11757,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="U58" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="V58" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W58" s="1" t="inlineStr">
@@ -12719,11 +11801,9 @@
 9:35</t>
         </is>
       </c>
-      <c r="AA58" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AB58" s="1" t="inlineStr">
@@ -12770,11 +11850,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="E59" s="1" t="inlineStr">
@@ -12801,11 +11879,9 @@
 8:37</t>
         </is>
       </c>
-      <c r="H59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="I59" s="1" t="inlineStr">
@@ -12833,18 +11909,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="L59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="M59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="N59" s="1" t="inlineStr">
@@ -12871,18 +11943,14 @@
 8:12</t>
         </is>
       </c>
-      <c r="Q59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="R59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="S59" s="1" t="inlineStr">
@@ -12917,32 +11985,24 @@
 8:00</t>
         </is>
       </c>
-      <c r="W59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="X59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="Y59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="Z59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AA59" s="1" t="inlineStr">
@@ -13005,18 +12065,14 @@
 8:22</t>
         </is>
       </c>
-      <c r="E60" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="F60" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="G60" s="1" t="inlineStr">
@@ -13035,18 +12091,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="I60" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="J60" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="K60" s="1" t="inlineStr">
@@ -13073,11 +12125,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="N60" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr">
@@ -13112,11 +12162,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="S60" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="T60" s="1" t="inlineStr">
@@ -13135,11 +12183,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="V60" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W60" s="1" t="inlineStr">
@@ -13167,11 +12213,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z60" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AA60" s="1" t="inlineStr">
@@ -13190,11 +12234,9 @@
 8:02</t>
         </is>
       </c>
-      <c r="AC60" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AD60" s="1" t="inlineStr">
@@ -13233,11 +12275,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="E61" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="F61" s="1" t="inlineStr">
@@ -13256,11 +12296,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="H61" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="I61" s="1" t="inlineStr">
@@ -13288,11 +12326,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="L61" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="M61" s="1" t="inlineStr">
@@ -13319,18 +12355,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="P61" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="Q61" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R61" s="1" t="inlineStr">
@@ -13365,11 +12397,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="V61" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W61" s="1" t="inlineStr">
@@ -13405,18 +12435,14 @@
 8:04</t>
         </is>
       </c>
-      <c r="AA61" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AB61" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC61" s="1" t="inlineStr">
@@ -13455,18 +12481,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="D62" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="E62" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="F62" s="1" t="inlineStr">
@@ -13518,11 +12540,9 @@
 8:04</t>
         </is>
       </c>
-      <c r="L62" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="M62" s="1" t="inlineStr">
@@ -13541,11 +12561,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="O62" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P62" s="1" t="inlineStr">
@@ -13564,18 +12582,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="R62" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="S62" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="T62" s="1" t="inlineStr">
@@ -13619,11 +12633,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Y62" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Z62" s="1" t="inlineStr">
@@ -13658,11 +12670,9 @@
 8:12</t>
         </is>
       </c>
-      <c r="AD62" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -13677,11 +12687,9 @@
           <t>馬苙櫞</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
@@ -13716,11 +12724,9 @@
 8:07</t>
         </is>
       </c>
-      <c r="H63" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="I63" s="1" t="inlineStr">
@@ -13756,18 +12762,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="M63" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="N63" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr">
@@ -13802,11 +12804,9 @@
 9:42</t>
         </is>
       </c>
-      <c r="S63" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="T63" s="1" t="inlineStr">
@@ -13825,11 +12825,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="V63" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W63" s="1" t="inlineStr">
@@ -13865,18 +12863,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA63" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AB63" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC63" s="1" t="inlineStr">
@@ -13907,11 +12901,9 @@
           <t>吳岱凝</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
@@ -13938,11 +12930,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="G64" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H64" s="1" t="inlineStr">
@@ -13962,11 +12952,9 @@
 8:52</t>
         </is>
       </c>
-      <c r="J64" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="K64" s="1" t="inlineStr">
@@ -13985,11 +12973,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="M64" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="N64" s="1" t="inlineStr">
@@ -14024,11 +13010,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="R64" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="S64" s="1" t="inlineStr">
@@ -14055,11 +13039,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="V64" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W64" s="1" t="inlineStr">
@@ -14095,18 +13077,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA64" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AB64" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC64" s="1" t="inlineStr">
@@ -14137,18 +13115,14 @@
           <t>柯家翔</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="E65" s="1" t="inlineStr">
@@ -14183,25 +13157,19 @@
 8:00</t>
         </is>
       </c>
-      <c r="I65" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="J65" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="K65" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO
-</t>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>DO</t>
         </is>
       </c>
       <c r="L65" s="1" t="inlineStr">
@@ -14220,18 +13188,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="N65" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="O65" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P65" s="1" t="inlineStr">
@@ -14266,11 +13230,9 @@
 9:42</t>
         </is>
       </c>
-      <c r="T65" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="U65" s="1" t="inlineStr">
@@ -14289,11 +13251,9 @@
 8:07</t>
         </is>
       </c>
-      <c r="W65" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="X65" s="1" t="inlineStr">
@@ -14313,18 +13273,14 @@
 9:02</t>
         </is>
       </c>
-      <c r="Z65" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AA65" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AB65" s="1" t="inlineStr">
@@ -14387,18 +13343,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="F66" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="G66" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H66" s="1" t="inlineStr">
@@ -14418,11 +13370,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="J66" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="K66" s="1" t="inlineStr">
@@ -14457,11 +13407,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="O66" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="P66" s="1" t="inlineStr">
@@ -14488,25 +13436,19 @@
 8:00</t>
         </is>
       </c>
-      <c r="S66" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="T66" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO
-</t>
-        </is>
-      </c>
-      <c r="U66" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="V66" s="1" t="inlineStr">
@@ -14558,25 +13500,19 @@
 8:00</t>
         </is>
       </c>
-      <c r="AB66" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AC66" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO
-</t>
-        </is>
-      </c>
-      <c r="AD66" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -14599,11 +13535,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="E67" s="1" t="inlineStr">
@@ -14622,11 +13556,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="G67" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="H67" s="1" t="inlineStr">
@@ -14654,17 +13586,15 @@
 8:00</t>
         </is>
       </c>
-      <c r="K67" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="L67" s="1" t="inlineStr">
         <is>
           <t>5:00
-E008g
+E008G
 13:30
 8:30</t>
         </is>
@@ -14693,18 +13623,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="P67" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
-        </is>
-      </c>
-      <c r="Q67" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R67" s="1" t="inlineStr">
@@ -14723,11 +13649,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="T67" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="U67" s="1" t="inlineStr">
@@ -14754,18 +13678,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="X67" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="Y67" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="Z67" s="1" t="inlineStr">
@@ -14784,11 +13704,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AB67" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC67" s="1" t="inlineStr">
@@ -14827,18 +13745,14 @@
 9:17</t>
         </is>
       </c>
-      <c r="D68" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="E68" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="F68" s="1" t="inlineStr">
@@ -14890,11 +13804,9 @@
 9:30</t>
         </is>
       </c>
-      <c r="L68" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="M68" s="1" t="inlineStr">
@@ -14921,11 +13833,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="P68" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="Q68" s="1" t="inlineStr">
@@ -14944,11 +13854,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="S68" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="T68" s="1" t="inlineStr">
@@ -14967,11 +13875,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="V68" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W68" s="1" t="inlineStr">
@@ -15016,25 +13922,19 @@
 8:00</t>
         </is>
       </c>
-      <c r="AB68" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="AC68" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
-        </is>
-      </c>
-      <c r="AD68" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
     </row>
@@ -15049,11 +13949,9 @@
           <t>邱奕庭</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr">
@@ -15088,11 +13986,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="H69" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="I69" s="1" t="inlineStr">
@@ -15112,18 +14008,14 @@
 8:07</t>
         </is>
       </c>
-      <c r="K69" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
-        </is>
-      </c>
-      <c r="L69" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="M69" s="1" t="inlineStr">
@@ -15166,11 +14058,9 @@
 9:30</t>
         </is>
       </c>
-      <c r="R69" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="S69" s="1" t="inlineStr">
@@ -15197,11 +14087,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="V69" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="W69" s="1" t="inlineStr">
@@ -15229,11 +14117,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z69" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO1
-</t>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AA69" s="1" t="inlineStr">
@@ -15260,11 +14146,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD69" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO3X
-</t>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
     </row>
@@ -15285,11 +14169,9 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
-      <c r="I70" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J70" t="inlineStr"/>
@@ -15306,11 +14188,9 @@
       <c r="U70" t="inlineStr"/>
       <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr"/>
-      <c r="X70" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr"/>
@@ -15337,11 +14217,9 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
-      <c r="I71" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J71" t="inlineStr"/>
@@ -15358,11 +14236,9 @@
       <c r="U71" t="inlineStr"/>
       <c r="V71" t="inlineStr"/>
       <c r="W71" t="inlineStr"/>
-      <c r="X71" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr"/>
@@ -15389,11 +14265,9 @@
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
-      <c r="I72" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J72" t="inlineStr"/>
@@ -15410,11 +14284,9 @@
       <c r="U72" t="inlineStr"/>
       <c r="V72" t="inlineStr"/>
       <c r="W72" t="inlineStr"/>
-      <c r="X72" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr"/>
@@ -15441,11 +14313,9 @@
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
-      <c r="I73" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J73" t="inlineStr"/>
@@ -15462,11 +14332,9 @@
       <c r="U73" t="inlineStr"/>
       <c r="V73" t="inlineStr"/>
       <c r="W73" t="inlineStr"/>
-      <c r="X73" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr"/>
@@ -15493,11 +14361,9 @@
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
-      <c r="I74" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J74" t="inlineStr"/>
@@ -15514,11 +14380,9 @@
       <c r="U74" t="inlineStr"/>
       <c r="V74" t="inlineStr"/>
       <c r="W74" t="inlineStr"/>
-      <c r="X74" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr"/>
@@ -15552,11 +14416,9 @@
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
-      <c r="I75" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J75" t="inlineStr"/>
@@ -15573,11 +14435,9 @@
       <c r="U75" t="inlineStr"/>
       <c r="V75" t="inlineStr"/>
       <c r="W75" t="inlineStr"/>
-      <c r="X75" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr"/>
@@ -15611,11 +14471,9 @@
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
-      <c r="I76" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J76" t="inlineStr"/>
@@ -15632,11 +14490,9 @@
       <c r="U76" t="inlineStr"/>
       <c r="V76" t="inlineStr"/>
       <c r="W76" t="inlineStr"/>
-      <c r="X76" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr"/>
@@ -15663,11 +14519,9 @@
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
-      <c r="I77" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J77" t="inlineStr"/>
@@ -15684,11 +14538,9 @@
       <c r="U77" t="inlineStr"/>
       <c r="V77" t="inlineStr"/>
       <c r="W77" t="inlineStr"/>
-      <c r="X77" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr"/>
@@ -15722,11 +14574,9 @@
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
-      <c r="I78" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J78" t="inlineStr"/>
@@ -15743,11 +14593,9 @@
       <c r="U78" t="inlineStr"/>
       <c r="V78" t="inlineStr"/>
       <c r="W78" t="inlineStr"/>
-      <c r="X78" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr"/>
@@ -15781,11 +14629,9 @@
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
-      <c r="I79" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J79" t="inlineStr"/>
@@ -15802,11 +14648,9 @@
       <c r="U79" t="inlineStr"/>
       <c r="V79" t="inlineStr"/>
       <c r="W79" t="inlineStr"/>
-      <c r="X79" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr"/>
@@ -15840,11 +14684,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="I80" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="J80" t="inlineStr"/>
@@ -15861,11 +14703,9 @@
       <c r="U80" t="inlineStr"/>
       <c r="V80" t="inlineStr"/>
       <c r="W80" t="inlineStr"/>
-      <c r="X80" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-DO2
-</t>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>DO2</t>
         </is>
       </c>
       <c r="Y80" s="1" t="inlineStr">

--- a/data/TTN/最新版班表/2026-10/TTN_TM.xlsx
+++ b/data/TTN/最新版班表/2026-10/TTN_TM.xlsx
@@ -890,14 +890,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="G7" s="1" t="inlineStr">
@@ -916,9 +920,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J7" s="1" t="inlineStr">
@@ -945,14 +951,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="M7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
@@ -971,9 +981,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Q7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="R7" s="1" t="inlineStr">
@@ -992,9 +1004,11 @@
 9:35</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="T7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="U7" s="1" t="inlineStr">
@@ -1021,19 +1035,25 @@
 8:00</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="X7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="Y7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="Z7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AA7" s="1" t="inlineStr">
@@ -1080,9 +1100,11 @@
           <t>汪莉芳</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
@@ -1117,14 +1139,18 @@
 8:22</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J8" s="1" t="inlineStr">
@@ -1143,14 +1169,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="L8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="N8" s="1" t="inlineStr">
@@ -1177,9 +1207,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Q8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr">
@@ -1206,9 +1238,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="U8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="V8" s="1" t="inlineStr">
@@ -1244,14 +1278,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="Z8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AA8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AB8" s="1" t="inlineStr">
@@ -1314,14 +1352,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="H9" s="1" t="inlineStr">
@@ -1357,9 +1399,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="L9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="M9" s="1" t="inlineStr">
@@ -1378,9 +1422,11 @@
 8:02</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="O9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr">
@@ -1407,9 +1453,11 @@
 9:12</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="S9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="T9" s="1" t="inlineStr">
@@ -1436,14 +1484,18 @@
 8:32</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="W9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="X9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y9" s="1" t="inlineStr">
@@ -1462,14 +1514,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AA9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AB9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AC9" s="1" t="inlineStr">
@@ -1516,9 +1572,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="F10" s="1" t="inlineStr">
@@ -1537,14 +1595,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="H10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J10" s="1" t="inlineStr">
@@ -1579,14 +1641,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="N10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="O10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr">
@@ -1605,9 +1671,11 @@
 8:02</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="R10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="S10" s="1" t="inlineStr">
@@ -1634,9 +1702,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="V10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="W10" s="1" t="inlineStr">
@@ -1656,9 +1726,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Y10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="Z10" s="1" t="inlineStr">
@@ -1693,9 +1765,11 @@
 8:35</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AD10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -1718,14 +1792,18 @@
 8:07</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="F11" s="1" t="inlineStr">
@@ -1761,9 +1839,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="J11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="K11" s="1" t="inlineStr">
@@ -1798,9 +1878,11 @@
 8:07</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="O11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr">
@@ -1835,14 +1917,18 @@
 8:22</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="T11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="U11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="V11" s="1" t="inlineStr">
@@ -1861,9 +1947,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="X11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y11" s="1" t="inlineStr">
@@ -1891,9 +1979,11 @@
 9:42</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="AB11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="AC11" s="1" t="inlineStr">
@@ -1932,14 +2022,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="F12" s="1" t="inlineStr">
@@ -1966,9 +2060,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="I12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J12" s="1" t="inlineStr">
@@ -1987,14 +2083,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="L12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="M12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="N12" s="1" t="inlineStr">
@@ -2021,9 +2121,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Q12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="R12" s="1" t="inlineStr">
@@ -2058,9 +2160,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="V12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="W12" s="1" t="inlineStr">
@@ -2088,14 +2192,18 @@
 8:05</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="Z12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AA12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AB12" s="1" t="inlineStr">
@@ -2150,9 +2258,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="F13" s="1" t="inlineStr">
@@ -2171,19 +2281,25 @@
 8:07</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="H13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="J13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="K13" s="1" t="inlineStr">
@@ -2202,9 +2318,11 @@
 8:22</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="M13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="N13" s="1" t="inlineStr">
@@ -2231,9 +2349,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Q13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="R13" s="1" t="inlineStr">
@@ -2268,9 +2388,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="V13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="W13" s="1" t="inlineStr">
@@ -2306,14 +2428,18 @@
 8:22</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AA13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AB13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AC13" s="1" t="inlineStr">
@@ -2352,14 +2478,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="F14" s="1" t="inlineStr">
@@ -2403,9 +2533,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="K14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr">
@@ -2440,9 +2572,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="P14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="Q14" s="1" t="inlineStr">
@@ -2461,14 +2595,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="S14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="T14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="U14" s="1" t="inlineStr">
@@ -2495,14 +2633,18 @@
 8:10</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="X14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="Y14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="Z14" s="1" t="inlineStr">
@@ -2529,9 +2671,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AC14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AD14" s="1" t="inlineStr">
@@ -2578,14 +2722,18 @@
 9:40</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="H15" s="1" t="inlineStr">
@@ -2613,9 +2761,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="K15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="L15" s="1" t="inlineStr">
@@ -2642,9 +2792,11 @@
 9:40</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="O15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr">
@@ -2679,14 +2831,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="T15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="U15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="V15" s="1" t="inlineStr">
@@ -2730,9 +2886,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="AA15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="AB15" s="1" t="inlineStr">
@@ -2751,9 +2909,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AD15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -2768,9 +2928,11 @@
           <t>李育真</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
@@ -2805,14 +2967,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="H16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="I16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J16" s="1" t="inlineStr">
@@ -2823,9 +2989,11 @@
 8:27</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="K16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="L16" s="1" t="inlineStr">
@@ -2836,9 +3004,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="M16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="N16" s="1" t="inlineStr">
@@ -2881,9 +3051,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="S16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="T16" s="1" t="inlineStr">
@@ -2910,14 +3082,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="W16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="X16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y16" s="1" t="inlineStr">
@@ -2936,9 +3112,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="AA16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="AB16" s="1" t="inlineStr">
@@ -3002,14 +3180,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="H17" s="1" t="inlineStr">
@@ -3053,14 +3235,18 @@
 9:40</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="M17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="N17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
@@ -3087,14 +3273,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="R17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="S17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="T17" s="1" t="inlineStr">
@@ -3138,14 +3328,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="Y17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="Z17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="AA17" s="1" t="inlineStr">
@@ -3172,9 +3366,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AD17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -3205,14 +3401,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="G18" s="1" t="inlineStr">
@@ -3231,9 +3431,11 @@
 9:52</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="I18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J18" s="1" t="inlineStr">
@@ -3252,15 +3454,17 @@
 8:00</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="L18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="M18" s="1" t="inlineStr">
         <is>
           <t>5:00
-E008G
+E008g
 13:30
 8:30</t>
         </is>
@@ -3281,9 +3485,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="P18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="Q18" s="1" t="inlineStr">
@@ -3318,14 +3524,18 @@
 8:10</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="U18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="V18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="W18" s="1" t="inlineStr">
@@ -3353,9 +3563,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Z18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="AA18" s="1" t="inlineStr">
@@ -3374,9 +3586,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AC18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AD18" s="1" t="inlineStr">
@@ -3415,14 +3629,18 @@
 9:42</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="G19" s="1" t="inlineStr">
@@ -3450,9 +3668,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="J19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="K19" s="1" t="inlineStr">
@@ -3495,9 +3715,11 @@
 9:35</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="P19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="Q19" s="1" t="inlineStr">
@@ -3516,14 +3738,18 @@
 9:35</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="S19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="T19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="U19" s="1" t="inlineStr">
@@ -3567,9 +3793,11 @@
 8:22</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Z19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="AA19" s="1" t="inlineStr">
@@ -3596,9 +3824,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AD19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -3621,9 +3851,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
@@ -3650,9 +3882,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="H20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="I20" s="1" t="inlineStr">
@@ -3688,14 +3922,18 @@
 8:10</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="M20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="N20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
@@ -3730,9 +3968,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="S20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="T20" s="1" t="inlineStr">
@@ -3751,9 +3991,11 @@
 8:27</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="V20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="W20" s="1" t="inlineStr">
@@ -3773,9 +4015,11 @@
 8:12</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Y20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="Z20" s="1" t="inlineStr">
@@ -3802,9 +4046,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AC20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AD20" s="1" t="inlineStr">
@@ -3835,14 +4081,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="F21" s="1" t="inlineStr">
@@ -3869,9 +4119,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="I21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J21" s="1" t="inlineStr">
@@ -3882,9 +4134,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="K21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="L21" s="1" t="inlineStr">
@@ -3919,14 +4173,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="P21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="Q21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="R21" s="1" t="inlineStr">
@@ -3953,9 +4211,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="U21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="V21" s="1" t="inlineStr">
@@ -3983,14 +4243,18 @@
 9:50</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="Y21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="Z21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AA21" s="1" t="inlineStr">
@@ -4045,9 +4309,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
@@ -4058,9 +4324,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="F22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="G22" s="1" t="inlineStr">
@@ -4079,9 +4347,11 @@
 8:20</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="I22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J22" s="1" t="inlineStr">
@@ -4108,9 +4378,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="M22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="N22" s="1" t="inlineStr">
@@ -4129,14 +4401,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="P22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="Q22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="R22" s="1" t="inlineStr">
@@ -4171,9 +4447,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="V22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="W22" s="1" t="inlineStr">
@@ -4201,14 +4479,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="Z22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AA22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AB22" s="1" t="inlineStr">
@@ -4247,9 +4529,11 @@
           <t>陳坤妏</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
@@ -4284,9 +4568,11 @@
 8:27</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="H23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="I23" s="1" t="inlineStr">
@@ -4314,14 +4600,18 @@
 8:15</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="L23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="M23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="N23" s="1" t="inlineStr">
@@ -4356,9 +4646,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="R23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="S23" s="1" t="inlineStr">
@@ -4393,14 +4685,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="W23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="X23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y23" s="1" t="inlineStr">
@@ -4419,14 +4715,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AA23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AB23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AC23" s="1" t="inlineStr">
@@ -4473,29 +4773,39 @@
 8:00</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="E24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="F24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="G24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="H24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="I24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J24" s="1" t="inlineStr">
@@ -4530,9 +4840,11 @@
 8:07</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="N24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
@@ -4543,9 +4855,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="P24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="Q24" s="1" t="inlineStr">
@@ -4564,9 +4878,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="S24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="T24" s="1" t="inlineStr">
@@ -4585,9 +4901,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="V24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="W24" s="1" t="inlineStr">
@@ -4598,9 +4916,11 @@
 8:15</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="X24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y24" s="1" t="inlineStr">
@@ -4627,14 +4947,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AB24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AC24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AD24" s="1" t="inlineStr">
@@ -4689,14 +5013,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="G25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="H25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="I25" s="1" t="inlineStr">
@@ -4740,14 +5068,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="N25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="O25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr">
@@ -4766,9 +5098,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="R25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="S25" s="1" t="inlineStr">
@@ -4803,9 +5137,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="W25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="X25" s="1" t="inlineStr">
@@ -4833,14 +5169,18 @@
 9:42</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AA25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AB25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AC25" s="1" t="inlineStr">
@@ -4879,9 +5219,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
@@ -4908,14 +5250,18 @@
 8:57</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="H26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="I26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J26" s="1" t="inlineStr">
@@ -4934,9 +5280,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="L26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="M26" s="1" t="inlineStr">
@@ -4955,9 +5303,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="O26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr">
@@ -4976,14 +5326,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="R26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="S26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="T26" s="1" t="inlineStr">
@@ -5018,9 +5372,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="X26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y26" s="1" t="inlineStr">
@@ -5031,9 +5387,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Z26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="AA26" s="1" t="inlineStr">
@@ -5060,9 +5418,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AD26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -5085,14 +5445,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="D27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="E27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="F27" s="1" t="inlineStr">
@@ -5128,9 +5492,11 @@
 9:30</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="J27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="K27" s="1" t="inlineStr">
@@ -5173,9 +5539,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="P27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="Q27" s="1" t="inlineStr">
@@ -5194,14 +5562,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="S27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="T27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="U27" s="1" t="inlineStr">
@@ -5245,14 +5617,18 @@
 9:57</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="Z27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AA27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AB27" s="1" t="inlineStr">
@@ -5291,9 +5667,11 @@
           <t>林怡宏</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="C28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
@@ -5328,9 +5706,11 @@
 9:55</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="H28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="I28" s="1" t="inlineStr">
@@ -5350,9 +5730,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="K28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="L28" s="1" t="inlineStr">
@@ -5371,9 +5753,11 @@
 9:35</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="N28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
@@ -5400,14 +5784,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="R28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="S28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="T28" s="1" t="inlineStr">
@@ -5442,19 +5830,25 @@
 8:00</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="X28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="Y28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="Z28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AA28" s="1" t="inlineStr">
@@ -5525,14 +5919,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="H29" s="1" t="inlineStr">
@@ -5543,9 +5941,11 @@
 8:10</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="I29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J29" s="1" t="inlineStr">
@@ -5556,14 +5956,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="K29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="L29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="M29" s="1" t="inlineStr">
@@ -5598,14 +6002,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="Q29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="R29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="S29" s="1" t="inlineStr">
@@ -5624,9 +6032,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="U29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="V29" s="1" t="inlineStr">
@@ -5654,9 +6064,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Y29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="Z29" s="1" t="inlineStr">
@@ -5691,9 +6103,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AD29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -5716,9 +6130,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
@@ -5737,9 +6153,11 @@
 8:22</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="G30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="H30" s="1" t="inlineStr">
@@ -5750,9 +6168,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="I30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J30" s="1" t="inlineStr">
@@ -5763,14 +6183,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="K30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="L30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="M30" s="1" t="inlineStr">
@@ -5813,14 +6237,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="R30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="S30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="T30" s="1" t="inlineStr">
@@ -5847,9 +6275,11 @@
 8:42</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="W30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="X30" s="1" t="inlineStr">
@@ -5869,14 +6299,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="Z30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AA30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AB30" s="1" t="inlineStr">
@@ -5923,9 +6357,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="D31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr">
@@ -5952,9 +6388,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="H31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="I31" s="1" t="inlineStr">
@@ -5974,9 +6412,11 @@
 8:12</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="K31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="L31" s="1" t="inlineStr">
@@ -6011,9 +6451,11 @@
 8:12</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="P31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="Q31" s="1" t="inlineStr">
@@ -6032,14 +6474,18 @@
 9:40</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="S31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="T31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="U31" s="1" t="inlineStr">
@@ -6075,9 +6521,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Y31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="Z31" s="1" t="inlineStr">
@@ -6112,9 +6560,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AD31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -6137,9 +6587,11 @@
 8:32</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr">
@@ -6158,9 +6610,11 @@
 8:22</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="G32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="H32" s="1" t="inlineStr">
@@ -6196,14 +6650,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="L32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="M32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="N32" s="1" t="inlineStr">
@@ -6238,9 +6696,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="R32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="S32" s="1" t="inlineStr">
@@ -6275,14 +6735,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="W32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="X32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y32" s="1" t="inlineStr">
@@ -6309,14 +6773,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AB32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AC32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AD32" s="1" t="inlineStr">
@@ -6347,9 +6815,11 @@
 8:12</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="D33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr">
@@ -6368,9 +6838,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="G33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="H33" s="1" t="inlineStr">
@@ -6422,14 +6894,18 @@
 9:40</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="N33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="O33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr">
@@ -6448,9 +6924,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="R33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="S33" s="1" t="inlineStr">
@@ -6469,9 +6947,11 @@
 9:35</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="U33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="V33" s="1" t="inlineStr">
@@ -6499,9 +6979,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Y33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="Z33" s="1" t="inlineStr">
@@ -6536,9 +7018,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AD33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -6569,14 +7053,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="E34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="F34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="G34" s="1" t="inlineStr">
@@ -6595,9 +7083,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="I34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J34" s="1" t="inlineStr">
@@ -6616,9 +7106,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="L34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="M34" s="1" t="inlineStr">
@@ -6637,9 +7129,11 @@
 8:02</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="O34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr">
@@ -6690,14 +7184,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="V34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="W34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="X34" s="1" t="inlineStr">
@@ -6733,14 +7231,18 @@
 8:22</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AB34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AC34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AD34" s="1" t="inlineStr">
@@ -6763,9 +7265,11 @@
           <t>林淮震</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
@@ -6784,9 +7288,11 @@
 8:10</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="F35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="G35" s="1" t="inlineStr">
@@ -6838,14 +7344,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="M35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="N35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
@@ -6888,9 +7398,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="T35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="U35" s="1" t="inlineStr">
@@ -6909,9 +7421,11 @@
 9:17</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="W35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="X35" s="1" t="inlineStr">
@@ -6955,14 +7469,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AC35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AD35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -6985,14 +7503,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="D36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="E36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="F36" s="1" t="inlineStr">
@@ -7003,19 +7525,25 @@
 8:00</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="G36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="H36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="I36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J36" s="1" t="inlineStr">
@@ -7026,9 +7554,11 @@
 8:12</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="K36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="L36" s="1" t="inlineStr">
@@ -7047,9 +7577,11 @@
 8:22</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="N36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
@@ -7092,14 +7624,18 @@
 8:10</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="T36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="U36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="V36" s="1" t="inlineStr">
@@ -7118,9 +7654,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="X36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y36" s="1" t="inlineStr">
@@ -7139,14 +7677,18 @@
 8:22</t>
         </is>
       </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AA36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AB36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AC36" s="1" t="inlineStr">
@@ -7193,14 +7735,18 @@
 8:22</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="E37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="F37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="G37" s="1" t="inlineStr">
@@ -7219,9 +7765,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="I37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J37" s="1" t="inlineStr">
@@ -7232,9 +7780,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="K37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="L37" s="1" t="inlineStr">
@@ -7261,9 +7811,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="O37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr">
@@ -7282,9 +7834,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="R37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="S37" s="1" t="inlineStr">
@@ -7319,9 +7873,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="W37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="X37" s="1" t="inlineStr">
@@ -7341,9 +7897,11 @@
 9:07</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Z37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="AA37" s="1" t="inlineStr">
@@ -7362,9 +7920,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AC37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AD37" s="1" t="inlineStr">
@@ -7387,9 +7947,11 @@
           <t>侯美玉</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
@@ -7408,9 +7970,11 @@
 9:42</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="F38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
@@ -7438,9 +8002,11 @@
 8:05</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="J38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="K38" s="1" t="inlineStr">
@@ -7467,9 +8033,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="N38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
@@ -7496,9 +8064,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="R38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="S38" s="1" t="inlineStr">
@@ -7525,9 +8095,11 @@
 9:35</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="V38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="W38" s="1" t="inlineStr">
@@ -7538,9 +8110,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="X38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y38" s="1" t="inlineStr">
@@ -7567,9 +8141,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="AB38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="AC38" s="1" t="inlineStr">
@@ -7580,9 +8156,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD38" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AD38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -7597,14 +8175,18 @@
           <t>林蕙儀</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="E39" s="1" t="inlineStr">
@@ -7623,9 +8205,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="G39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="H39" s="1" t="inlineStr">
@@ -7653,14 +8237,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="K39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="L39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="M39" s="1" t="inlineStr">
@@ -7695,9 +8283,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Q39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="R39" s="1" t="inlineStr">
@@ -7740,14 +8330,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="W39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="X39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y39" s="1" t="inlineStr">
@@ -7766,19 +8360,25 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AA39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="AB39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AC39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AD39" s="1" t="inlineStr">
@@ -7801,9 +8401,11 @@
           <t>徐玓瑋</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="C40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
@@ -7822,9 +8424,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="F40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr">
@@ -7843,9 +8447,11 @@
 8:27</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="I40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J40" s="1" t="inlineStr">
@@ -7864,14 +8470,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="L40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="M40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="N40" s="1" t="inlineStr">
@@ -7914,9 +8524,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="S40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="T40" s="1" t="inlineStr">
@@ -7935,9 +8547,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="V40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="W40" s="1" t="inlineStr">
@@ -7973,14 +8587,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AA40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AB40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AC40" s="1" t="inlineStr">
@@ -8011,9 +8629,11 @@
           <t>陳君煒</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="C41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
@@ -8048,14 +8668,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="H41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="I41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J41" s="1" t="inlineStr">
@@ -8082,14 +8706,18 @@
 8:22</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="M41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="N41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr">
@@ -8132,14 +8760,18 @@
 8:16</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="T41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="U41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="V41" s="1" t="inlineStr">
@@ -8175,14 +8807,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="Z41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AA41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AB41" s="1" t="inlineStr">
@@ -8201,9 +8837,11 @@
 8:07</t>
         </is>
       </c>
-      <c r="AD41" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="AD41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
     </row>
@@ -8218,9 +8856,11 @@
           <t>郭曉芸</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
@@ -8247,9 +8887,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="G42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="H42" s="1" t="inlineStr">
@@ -8285,9 +8927,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="L42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="M42" s="1" t="inlineStr">
@@ -8314,14 +8958,18 @@
 8:32</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="P42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="Q42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="R42" s="1" t="inlineStr">
@@ -8356,9 +9004,11 @@
 8:02</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="V42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="W42" s="1" t="inlineStr">
@@ -8394,9 +9044,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="AA42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="AB42" s="1" t="inlineStr">
@@ -8407,9 +9059,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AC42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AD42" s="1" t="inlineStr">
@@ -8440,9 +9094,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="D43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
@@ -8469,9 +9125,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="H43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="I43" s="1" t="inlineStr">
@@ -8499,14 +9157,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="L43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="M43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="N43" s="1" t="inlineStr">
@@ -8549,14 +9211,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="S43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="T43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="U43" s="1" t="inlineStr">
@@ -8601,9 +9267,11 @@
 9:56</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Z43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="AA43" s="1" t="inlineStr">
@@ -8650,9 +9318,11 @@
           <t>李育瑋</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
@@ -8671,9 +9341,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="F44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="G44" s="1" t="inlineStr">
@@ -8717,14 +9389,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="L44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="M44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="N44" s="1" t="inlineStr">
@@ -8751,9 +9427,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Q44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="R44" s="1" t="inlineStr">
@@ -8780,9 +9458,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="U44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="V44" s="1" t="inlineStr">
@@ -8818,9 +9498,11 @@
 8:14</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Z44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="AA44" s="1" t="inlineStr">
@@ -8839,9 +9521,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AC44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AD44" s="1" t="inlineStr">
@@ -8872,9 +9556,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="D45" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="E45" s="1" t="inlineStr">
@@ -8901,9 +9587,11 @@
 8:35</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="H45" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="I45" s="1" t="inlineStr">
@@ -8931,9 +9619,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="L45" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="M45" s="1" t="inlineStr">
@@ -8952,9 +9642,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="O45" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="P45" s="1" t="inlineStr">
@@ -8973,9 +9665,11 @@
 9:17</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="R45" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="S45" s="1" t="inlineStr">
@@ -9010,9 +9704,11 @@
 9:40</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="W45" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="X45" s="1" t="inlineStr">
@@ -9040,9 +9736,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="AA45" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="AB45" s="1" t="inlineStr">
@@ -9082,9 +9780,11 @@
           <t>陳家豪</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
@@ -9103,9 +9803,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="F46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="G46" s="1" t="inlineStr">
@@ -9133,9 +9835,11 @@
 9:30</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="J46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="K46" s="1" t="inlineStr">
@@ -9170,9 +9874,11 @@
 8:07</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="O46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="P46" s="1" t="inlineStr">
@@ -9199,14 +9905,18 @@
 8:15</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="S46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="T46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="U46" s="1" t="inlineStr">
@@ -9242,9 +9952,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Y46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="Z46" s="1" t="inlineStr">
@@ -9263,19 +9975,25 @@
 8:00</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AB46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO
+</t>
+        </is>
+      </c>
+      <c r="AC46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO
+</t>
+        </is>
+      </c>
+      <c r="AD46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -9306,14 +10024,18 @@
 8:04</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="E47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="F47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="G47" s="1" t="inlineStr">
@@ -9349,9 +10071,11 @@
 9:54</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="K47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="L47" s="1" t="inlineStr">
@@ -9386,9 +10110,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="P47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="Q47" s="1" t="inlineStr">
@@ -9423,14 +10149,18 @@
 8:04</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="U47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="V47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="W47" s="1" t="inlineStr">
@@ -9458,9 +10188,11 @@
 9:25</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Z47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="AA47" s="1" t="inlineStr">
@@ -9487,9 +10219,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD47" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AD47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -9520,14 +10254,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="E48" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="F48" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="G48" s="1" t="inlineStr">
@@ -9546,9 +10284,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="I48" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J48" s="1" t="inlineStr">
@@ -9559,9 +10299,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="K48" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="L48" s="1" t="inlineStr">
@@ -9588,9 +10330,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="O48" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="P48" s="1" t="inlineStr">
@@ -9625,14 +10369,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="T48" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="U48" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="V48" s="1" t="inlineStr">
@@ -9684,14 +10432,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AB48" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AC48" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AD48" s="1" t="inlineStr">
@@ -9722,9 +10474,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="D49" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="E49" s="1" t="inlineStr">
@@ -9751,9 +10505,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="H49" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="I49" s="1" t="inlineStr">
@@ -9773,14 +10529,18 @@
 8:32</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="K49" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="L49" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="M49" s="1" t="inlineStr">
@@ -9823,14 +10583,18 @@
 9:44</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="R49" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="S49" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="T49" s="1" t="inlineStr">
@@ -9874,9 +10638,11 @@
 9:44</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Y49" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="Z49" s="1" t="inlineStr">
@@ -9911,9 +10677,11 @@
 8:02</t>
         </is>
       </c>
-      <c r="AD49" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AD49" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -9944,9 +10712,11 @@
 9:12</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="E50" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="F50" s="1" t="inlineStr">
@@ -9957,9 +10727,11 @@
 9:40</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="G50" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="H50" s="1" t="inlineStr">
@@ -10003,14 +10775,18 @@
 9:35</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="M50" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="N50" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr">
@@ -10037,9 +10813,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="R50" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="S50" s="1" t="inlineStr">
@@ -10066,9 +10844,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="V50" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="W50" s="1" t="inlineStr">
@@ -10088,9 +10868,11 @@
 8:02</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Y50" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="Z50" s="1" t="inlineStr">
@@ -10101,9 +10883,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AA50" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AB50" s="1" t="inlineStr">
@@ -10166,14 +10950,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="F51" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="G51" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="H51" s="1" t="inlineStr">
@@ -10217,9 +11005,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="M51" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="N51" s="1" t="inlineStr">
@@ -10238,29 +11028,39 @@
 8:00</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="P51" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="Q51" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="R51" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="S51" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="T51" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="U51" s="1" t="inlineStr">
@@ -10304,9 +11104,11 @@
 9:30</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Z51" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="AA51" s="1" t="inlineStr">
@@ -10333,9 +11135,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD51" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AD51" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -10350,9 +11154,11 @@
           <t>楊凱傑</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="D52" s="1" t="inlineStr">
@@ -10371,9 +11177,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="F52" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="G52" s="1" t="inlineStr">
@@ -10409,9 +11217,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="K52" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="L52" s="1" t="inlineStr">
@@ -10446,9 +11256,11 @@
 8:02</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="P52" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="Q52" s="1" t="inlineStr">
@@ -10459,9 +11271,11 @@
 8:22</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="R52" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="S52" s="1" t="inlineStr">
@@ -10480,9 +11294,11 @@
 8:16</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="U52" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="V52" s="1" t="inlineStr">
@@ -10501,9 +11317,11 @@
 8:02</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="X52" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y52" s="1" t="inlineStr">
@@ -10514,9 +11332,11 @@
 8:12</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Z52" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="AA52" s="1" t="inlineStr">
@@ -10535,9 +11355,11 @@
 8:32</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AC52" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AD52" s="1" t="inlineStr">
@@ -10560,9 +11382,11 @@
           <t>黃孟慈</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
@@ -10589,9 +11413,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="G53" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="H53" s="1" t="inlineStr">
@@ -10627,9 +11453,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="L53" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="M53" s="1" t="inlineStr">
@@ -10648,9 +11476,11 @@
 9:35</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="O53" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="P53" s="1" t="inlineStr">
@@ -10677,14 +11507,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="S53" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="T53" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="U53" s="1" t="inlineStr">
@@ -10711,9 +11545,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="X53" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y53" s="1" t="inlineStr">
@@ -10724,14 +11560,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="Z53" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AA53" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AB53" s="1" t="inlineStr">
@@ -10770,9 +11610,11 @@
           <t>劉芳毓</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="D54" s="1" t="inlineStr">
@@ -10791,9 +11633,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="F54" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="G54" s="1" t="inlineStr">
@@ -10829,9 +11673,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="K54" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="L54" s="1" t="inlineStr">
@@ -10858,9 +11704,11 @@
 8:32</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="O54" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="P54" s="1" t="inlineStr">
@@ -10887,14 +11735,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="S54" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="T54" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="U54" s="1" t="inlineStr">
@@ -10938,9 +11790,11 @@
 9:50</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Z54" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="AA54" s="1" t="inlineStr">
@@ -10951,9 +11805,11 @@
 8:16</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AB54" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AC54" s="1" t="inlineStr">
@@ -10992,14 +11848,18 @@
 9:30</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="D55" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="E55" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="F55" s="1" t="inlineStr">
@@ -11043,9 +11903,11 @@
 9:30</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="K55" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="L55" s="1" t="inlineStr">
@@ -11080,9 +11942,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="P55" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="Q55" s="1" t="inlineStr">
@@ -11101,14 +11965,18 @@
 8:22</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="S55" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="T55" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="U55" s="1" t="inlineStr">
@@ -11144,9 +12012,11 @@
 8:32</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Y55" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="Z55" s="1" t="inlineStr">
@@ -11183,9 +12053,11 @@
 9:35</t>
         </is>
       </c>
-      <c r="AD55" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="AD55" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
     </row>
@@ -11200,9 +12072,11 @@
           <t>曾智君</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="D56" s="1" t="inlineStr">
@@ -11229,9 +12103,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="G56" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="H56" s="1" t="inlineStr">
@@ -11275,9 +12151,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="M56" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="N56" s="1" t="inlineStr">
@@ -11288,9 +12166,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="O56" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="P56" s="1" t="inlineStr">
@@ -11325,9 +12205,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="T56" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="U56" s="1" t="inlineStr">
@@ -11346,9 +12228,11 @@
 9:35</t>
         </is>
       </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="W56" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="X56" s="1" t="inlineStr">
@@ -11376,9 +12260,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="AA56" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="AB56" s="1" t="inlineStr">
@@ -11417,9 +12303,11 @@
           <t>黃祥恩</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="D57" s="1" t="inlineStr">
@@ -11446,9 +12334,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="G57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="H57" s="1" t="inlineStr">
@@ -11476,14 +12366,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="K57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="L57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="M57" s="1" t="inlineStr">
@@ -11518,9 +12412,11 @@
 8:45</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Q57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="R57" s="1" t="inlineStr">
@@ -11547,9 +12443,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="U57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="V57" s="1" t="inlineStr">
@@ -11568,14 +12466,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="X57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="Y57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="Z57" s="1" t="inlineStr">
@@ -11586,14 +12488,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AA57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO
+</t>
+        </is>
+      </c>
+      <c r="AB57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AC57" s="1" t="inlineStr">
@@ -11640,14 +12546,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="E58" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="F58" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="G58" s="1" t="inlineStr">
@@ -11683,9 +12593,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="K58" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="L58" s="1" t="inlineStr">
@@ -11720,9 +12632,11 @@
 8:07</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="P58" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="Q58" s="1" t="inlineStr">
@@ -11757,14 +12671,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="U58" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="V58" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="W58" s="1" t="inlineStr">
@@ -11801,9 +12719,11 @@
 9:35</t>
         </is>
       </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="AA58" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="AB58" s="1" t="inlineStr">
@@ -11850,9 +12770,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="D59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="E59" s="1" t="inlineStr">
@@ -11879,9 +12801,11 @@
 8:37</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="H59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="I59" s="1" t="inlineStr">
@@ -11909,14 +12833,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="L59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="M59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="N59" s="1" t="inlineStr">
@@ -11943,14 +12871,18 @@
 8:12</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Q59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="R59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="S59" s="1" t="inlineStr">
@@ -11985,24 +12917,32 @@
 8:00</t>
         </is>
       </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="W59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="X59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="Y59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="Z59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AA59" s="1" t="inlineStr">
@@ -12065,14 +13005,18 @@
 8:22</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="E60" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="F60" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="G60" s="1" t="inlineStr">
@@ -12091,14 +13035,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="I60" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="J60" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="K60" s="1" t="inlineStr">
@@ -12125,9 +13073,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="N60" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr">
@@ -12162,9 +13112,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="S60" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="T60" s="1" t="inlineStr">
@@ -12183,9 +13135,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="V60" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="W60" s="1" t="inlineStr">
@@ -12213,9 +13167,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Z60" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="AA60" s="1" t="inlineStr">
@@ -12234,9 +13190,11 @@
 8:02</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AC60" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AD60" s="1" t="inlineStr">
@@ -12275,9 +13233,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="E61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="F61" s="1" t="inlineStr">
@@ -12296,9 +13256,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="H61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="I61" s="1" t="inlineStr">
@@ -12326,9 +13288,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="L61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="M61" s="1" t="inlineStr">
@@ -12355,14 +13319,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="P61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="Q61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="R61" s="1" t="inlineStr">
@@ -12397,9 +13365,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="V61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="W61" s="1" t="inlineStr">
@@ -12435,14 +13405,18 @@
 8:04</t>
         </is>
       </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AA61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AB61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AC61" s="1" t="inlineStr">
@@ -12481,14 +13455,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="D62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="E62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="F62" s="1" t="inlineStr">
@@ -12540,9 +13518,11 @@
 8:04</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="L62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="M62" s="1" t="inlineStr">
@@ -12561,9 +13541,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="O62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="P62" s="1" t="inlineStr">
@@ -12582,14 +13564,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="R62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="S62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="T62" s="1" t="inlineStr">
@@ -12633,9 +13619,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Y62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="Z62" s="1" t="inlineStr">
@@ -12670,9 +13658,11 @@
 8:12</t>
         </is>
       </c>
-      <c r="AD62" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AD62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -12687,9 +13677,11 @@
           <t>馬苙櫞</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
@@ -12724,9 +13716,11 @@
 8:07</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="H63" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="I63" s="1" t="inlineStr">
@@ -12762,14 +13756,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="M63" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="N63" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr">
@@ -12804,9 +13802,11 @@
 9:42</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="S63" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="T63" s="1" t="inlineStr">
@@ -12825,9 +13825,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="V63" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="W63" s="1" t="inlineStr">
@@ -12863,14 +13865,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AA63" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AB63" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AC63" s="1" t="inlineStr">
@@ -12901,9 +13907,11 @@
           <t>吳岱凝</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="C64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
@@ -12930,9 +13938,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="G64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="H64" s="1" t="inlineStr">
@@ -12952,9 +13962,11 @@
 8:52</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="J64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="K64" s="1" t="inlineStr">
@@ -12973,9 +13985,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="M64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="N64" s="1" t="inlineStr">
@@ -13010,9 +14024,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="R64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="S64" s="1" t="inlineStr">
@@ -13039,9 +14055,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="V64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="W64" s="1" t="inlineStr">
@@ -13077,14 +14095,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AA64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AB64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AC64" s="1" t="inlineStr">
@@ -13115,14 +14137,18 @@
           <t>柯家翔</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="C65" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="D65" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="E65" s="1" t="inlineStr">
@@ -13157,19 +14183,25 @@
 8:00</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>DO</t>
+      <c r="I65" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="J65" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="K65" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO
+</t>
         </is>
       </c>
       <c r="L65" s="1" t="inlineStr">
@@ -13188,14 +14220,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="N65" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="O65" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="P65" s="1" t="inlineStr">
@@ -13230,9 +14266,11 @@
 9:42</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="T65" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="U65" s="1" t="inlineStr">
@@ -13251,9 +14289,11 @@
 8:07</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="W65" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="X65" s="1" t="inlineStr">
@@ -13273,14 +14313,18 @@
 9:02</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="Z65" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AA65" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AB65" s="1" t="inlineStr">
@@ -13343,14 +14387,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="F66" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="G66" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="H66" s="1" t="inlineStr">
@@ -13370,9 +14418,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="J66" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="K66" s="1" t="inlineStr">
@@ -13407,9 +14457,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="O66" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="P66" s="1" t="inlineStr">
@@ -13436,19 +14488,25 @@
 8:00</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="S66" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="T66" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO
+</t>
+        </is>
+      </c>
+      <c r="U66" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="V66" s="1" t="inlineStr">
@@ -13500,19 +14558,25 @@
 8:00</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="AD66" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AB66" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AC66" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO
+</t>
+        </is>
+      </c>
+      <c r="AD66" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -13535,9 +14599,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="D67" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="E67" s="1" t="inlineStr">
@@ -13556,9 +14622,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="G67" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="H67" s="1" t="inlineStr">
@@ -13586,15 +14654,17 @@
 8:00</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="K67" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="L67" s="1" t="inlineStr">
         <is>
           <t>5:00
-E008G
+E008g
 13:30
 8:30</t>
         </is>
@@ -13623,14 +14693,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="P67" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
+        </is>
+      </c>
+      <c r="Q67" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="R67" s="1" t="inlineStr">
@@ -13649,9 +14723,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="T67" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="U67" s="1" t="inlineStr">
@@ -13678,14 +14754,18 @@
 8:00</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="X67" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="Y67" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="Z67" s="1" t="inlineStr">
@@ -13704,9 +14784,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AB67" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="AC67" s="1" t="inlineStr">
@@ -13745,14 +14827,18 @@
 9:17</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="D68" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="E68" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="F68" s="1" t="inlineStr">
@@ -13804,9 +14890,11 @@
 9:30</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="L68" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="M68" s="1" t="inlineStr">
@@ -13833,9 +14921,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="P68" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="Q68" s="1" t="inlineStr">
@@ -13854,9 +14944,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="S68" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="T68" s="1" t="inlineStr">
@@ -13875,9 +14967,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="V68" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="W68" s="1" t="inlineStr">
@@ -13922,19 +15016,25 @@
 8:00</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="AD68" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="AB68" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="AC68" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
+        </is>
+      </c>
+      <c r="AD68" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
     </row>
@@ -13949,9 +15049,11 @@
           <t>邱奕庭</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="C69" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr">
@@ -13986,9 +15088,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="H69" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="I69" s="1" t="inlineStr">
@@ -14008,14 +15112,18 @@
 8:07</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="K69" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
+        </is>
+      </c>
+      <c r="L69" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="M69" s="1" t="inlineStr">
@@ -14058,9 +15166,11 @@
 9:30</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="R69" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="S69" s="1" t="inlineStr">
@@ -14087,9 +15197,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="V69" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
       <c r="W69" s="1" t="inlineStr">
@@ -14117,9 +15229,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Z69" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO1
+</t>
         </is>
       </c>
       <c r="AA69" s="1" t="inlineStr">
@@ -14146,9 +15260,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="AD69" t="inlineStr">
-        <is>
-          <t>DO3X</t>
+      <c r="AD69" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO3X
+</t>
         </is>
       </c>
     </row>
@@ -14169,9 +15285,11 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="I70" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J70" t="inlineStr"/>
@@ -14188,9 +15306,11 @@
       <c r="U70" t="inlineStr"/>
       <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr"/>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="X70" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr"/>
@@ -14217,9 +15337,11 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="I71" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J71" t="inlineStr"/>
@@ -14236,9 +15358,11 @@
       <c r="U71" t="inlineStr"/>
       <c r="V71" t="inlineStr"/>
       <c r="W71" t="inlineStr"/>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="X71" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr"/>
@@ -14265,9 +15389,11 @@
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="I72" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J72" t="inlineStr"/>
@@ -14284,9 +15410,11 @@
       <c r="U72" t="inlineStr"/>
       <c r="V72" t="inlineStr"/>
       <c r="W72" t="inlineStr"/>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="X72" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr"/>
@@ -14313,9 +15441,11 @@
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="I73" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J73" t="inlineStr"/>
@@ -14332,9 +15462,11 @@
       <c r="U73" t="inlineStr"/>
       <c r="V73" t="inlineStr"/>
       <c r="W73" t="inlineStr"/>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="X73" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr"/>
@@ -14361,9 +15493,11 @@
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="I74" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J74" t="inlineStr"/>
@@ -14380,9 +15514,11 @@
       <c r="U74" t="inlineStr"/>
       <c r="V74" t="inlineStr"/>
       <c r="W74" t="inlineStr"/>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="X74" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr"/>
@@ -14416,9 +15552,11 @@
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="I75" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J75" t="inlineStr"/>
@@ -14435,9 +15573,11 @@
       <c r="U75" t="inlineStr"/>
       <c r="V75" t="inlineStr"/>
       <c r="W75" t="inlineStr"/>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="X75" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr"/>
@@ -14471,9 +15611,11 @@
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="I76" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J76" t="inlineStr"/>
@@ -14490,9 +15632,11 @@
       <c r="U76" t="inlineStr"/>
       <c r="V76" t="inlineStr"/>
       <c r="W76" t="inlineStr"/>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="X76" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr"/>
@@ -14519,9 +15663,11 @@
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="I77" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J77" t="inlineStr"/>
@@ -14538,9 +15684,11 @@
       <c r="U77" t="inlineStr"/>
       <c r="V77" t="inlineStr"/>
       <c r="W77" t="inlineStr"/>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="X77" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr"/>
@@ -14574,9 +15722,11 @@
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="I78" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J78" t="inlineStr"/>
@@ -14593,9 +15743,11 @@
       <c r="U78" t="inlineStr"/>
       <c r="V78" t="inlineStr"/>
       <c r="W78" t="inlineStr"/>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="X78" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr"/>
@@ -14629,9 +15781,11 @@
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="I79" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J79" t="inlineStr"/>
@@ -14648,9 +15802,11 @@
       <c r="U79" t="inlineStr"/>
       <c r="V79" t="inlineStr"/>
       <c r="W79" t="inlineStr"/>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="X79" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr"/>
@@ -14684,9 +15840,11 @@
 8:00</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="I80" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="J80" t="inlineStr"/>
@@ -14703,9 +15861,11 @@
       <c r="U80" t="inlineStr"/>
       <c r="V80" t="inlineStr"/>
       <c r="W80" t="inlineStr"/>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>DO2</t>
+      <c r="X80" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+DO2
+</t>
         </is>
       </c>
       <c r="Y80" s="1" t="inlineStr">
